--- a/research/traditional_assets/database/data/denmark/denmark_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_investments_asset_management.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.207</v>
+        <v>-0.0638</v>
       </c>
       <c r="E2">
-        <v>0.199</v>
+        <v>-0.123</v>
       </c>
       <c r="G2">
-        <v>-0.05693987358303296</v>
+        <v>-0.3528708133971292</v>
       </c>
       <c r="H2">
-        <v>-0.05693987358303296</v>
+        <v>-0.3528708133971292</v>
       </c>
       <c r="I2">
-        <v>0.8830179194049396</v>
+        <v>0.2625702018942228</v>
       </c>
       <c r="J2">
-        <v>0.881546222872598</v>
+        <v>0.2500981173042472</v>
       </c>
       <c r="K2">
-        <v>14.33</v>
+        <v>0.7940000000000002</v>
       </c>
       <c r="L2">
-        <v>0.7485765031604242</v>
+        <v>0.1582934609250399</v>
       </c>
       <c r="M2">
-        <v>8.050000000000001</v>
+        <v>0.889</v>
       </c>
       <c r="N2">
-        <v>0.09705811429949363</v>
+        <v>0.01234722222222222</v>
       </c>
       <c r="O2">
-        <v>0.561758548499651</v>
+        <v>1.119647355163728</v>
       </c>
       <c r="P2">
-        <v>8.050000000000001</v>
+        <v>0.889</v>
       </c>
       <c r="Q2">
-        <v>0.09705811429949363</v>
+        <v>0.01234722222222222</v>
       </c>
       <c r="R2">
-        <v>0.561758548499651</v>
+        <v>1.119647355163728</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>11.149</v>
+        <v>10.21</v>
       </c>
       <c r="V2">
-        <v>0.1344224740776465</v>
+        <v>0.1418055555555556</v>
       </c>
       <c r="W2">
-        <v>-0.07831858407079646</v>
+        <v>-0.02273291925465838</v>
       </c>
       <c r="X2">
-        <v>0.04387609615994809</v>
+        <v>0.07246641599770315</v>
       </c>
       <c r="Y2">
-        <v>-0.1221946802307446</v>
+        <v>-0.09519933525236153</v>
       </c>
       <c r="Z2">
-        <v>0.2921616796683917</v>
+        <v>0.0572857779148251</v>
       </c>
       <c r="AA2">
-        <v>-0.02094545454545454</v>
+        <v>-0.03748317631224764</v>
       </c>
       <c r="AB2">
-        <v>0.04387296409148227</v>
+        <v>0.07245268461371759</v>
       </c>
       <c r="AC2">
-        <v>-0.06481841863693681</v>
+        <v>-0.1099373953529525</v>
       </c>
       <c r="AD2">
-        <v>16.3</v>
+        <v>13.9</v>
       </c>
       <c r="AE2">
-        <v>0.001939844156215004</v>
+        <v>0.004739336492890996</v>
       </c>
       <c r="AF2">
-        <v>16.30193984415622</v>
+        <v>13.90473933649289</v>
       </c>
       <c r="AG2">
-        <v>5.152939844156217</v>
+        <v>3.694739336492891</v>
       </c>
       <c r="AH2">
-        <v>0.1642646230994259</v>
+        <v>0.1618623075267987</v>
       </c>
       <c r="AI2">
-        <v>0.1652972945970924</v>
+        <v>0.1779812573403088</v>
       </c>
       <c r="AJ2">
-        <v>0.05849435667911865</v>
+        <v>0.04881104511197695</v>
       </c>
       <c r="AK2">
-        <v>0.05890895919740222</v>
+        <v>0.05440261381534277</v>
       </c>
       <c r="AL2">
-        <v>0.487</v>
+        <v>0.344</v>
       </c>
       <c r="AM2">
-        <v>0.487</v>
+        <v>0.344</v>
       </c>
       <c r="AN2">
-        <v>-11.57670454545455</v>
+        <v>-8.501529051987768</v>
       </c>
       <c r="AO2">
-        <v>34.70636550308009</v>
+        <v>3.816860465116278</v>
       </c>
       <c r="AP2">
-        <v>-3.659758412042768</v>
+        <v>-2.259779410699016</v>
       </c>
       <c r="AQ2">
-        <v>34.70636550308009</v>
+        <v>3.816860465116278</v>
       </c>
     </row>
     <row r="3">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.207</v>
+        <v>-0.0638</v>
       </c>
       <c r="E3">
-        <v>0.199</v>
+        <v>-0.123</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,34 +734,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.9538461538461539</v>
+        <v>0.8345153664302599</v>
       </c>
       <c r="J3">
-        <v>0.9490769230769232</v>
+        <v>0.7155969267139479</v>
       </c>
       <c r="K3">
-        <v>18.1</v>
+        <v>2.74</v>
       </c>
       <c r="L3">
-        <v>0.9282051282051282</v>
+        <v>0.6477541371158392</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>0.889</v>
       </c>
       <c r="N3">
-        <v>0.01701782820097245</v>
+        <v>0.01514480408858603</v>
       </c>
       <c r="O3">
-        <v>0.0580110497237569</v>
+        <v>0.3244525547445255</v>
       </c>
       <c r="P3">
-        <v>1.05</v>
+        <v>0.889</v>
       </c>
       <c r="Q3">
-        <v>0.01701782820097245</v>
+        <v>0.01514480408858603</v>
       </c>
       <c r="R3">
-        <v>0.0580110497237569</v>
+        <v>0.3244525547445255</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,67 +770,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.899</v>
+        <v>2.02</v>
       </c>
       <c r="V3">
-        <v>0.01457050243111831</v>
+        <v>0.03441226575809199</v>
       </c>
       <c r="W3">
-        <v>0.4436274509803922</v>
+        <v>0.04781849912739965</v>
       </c>
       <c r="X3">
-        <v>0.04980196677315335</v>
+        <v>0.07867021636335089</v>
       </c>
       <c r="Y3">
-        <v>0.3938254842072389</v>
+        <v>-0.03085171723595124</v>
       </c>
       <c r="Z3">
-        <v>0.3766660227931234</v>
+        <v>0.05818351879616512</v>
       </c>
       <c r="AA3">
-        <v>0.3574850299401198</v>
+        <v>0.04163594723593899</v>
       </c>
       <c r="AB3">
-        <v>0.04320004906050148</v>
+        <v>0.07067173967670383</v>
       </c>
       <c r="AC3">
-        <v>0.3142849808796183</v>
+        <v>-0.02903579244076484</v>
       </c>
       <c r="AD3">
-        <v>16.3</v>
+        <v>13.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>16.3</v>
+        <v>13.9</v>
       </c>
       <c r="AG3">
-        <v>15.401</v>
+        <v>11.88</v>
       </c>
       <c r="AH3">
-        <v>0.208974358974359</v>
+        <v>0.1914600550964187</v>
       </c>
       <c r="AI3">
-        <v>0.2214673913043479</v>
+        <v>0.2227564102564103</v>
       </c>
       <c r="AJ3">
-        <v>0.1997509759925293</v>
+        <v>0.1683196372910173</v>
       </c>
       <c r="AK3">
-        <v>0.2118402773001747</v>
+        <v>0.1967538920172243</v>
       </c>
       <c r="AL3">
-        <v>0.453</v>
+        <v>0.328</v>
       </c>
       <c r="AM3">
-        <v>0.453</v>
+        <v>0.328</v>
       </c>
       <c r="AO3">
-        <v>41.05960264900663</v>
+        <v>10.76219512195122</v>
       </c>
       <c r="AQ3">
-        <v>41.05960264900663</v>
+        <v>10.76219512195122</v>
       </c>
     </row>
     <row r="4">
@@ -850,58 +850,55 @@
         </is>
       </c>
       <c r="K4">
-        <v>-1.77</v>
+        <v>-0.366</v>
       </c>
       <c r="M4">
-        <v>7</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.9536784741144414</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-3.954802259887006</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>7</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.9536784741144414</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>-3.954802259887006</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>1.24</v>
+        <v>2.24</v>
       </c>
       <c r="V4">
-        <v>0.1689373297002725</v>
+        <v>0.7225806451612904</v>
       </c>
       <c r="W4">
-        <v>-0.07831858407079646</v>
+        <v>-0.02273291925465838</v>
       </c>
       <c r="X4">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y4">
-        <v>-0.1221915481622787</v>
+        <v>-0.09518713829536324</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.02094545454545454</v>
+        <v>-0.03748317631224764</v>
       </c>
       <c r="AB4">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC4">
-        <v>-0.06481841863693681</v>
+        <v>-0.1099373953529525</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -913,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-1.24</v>
+        <v>-2.24</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -922,22 +919,22 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.2032786885245902</v>
+        <v>-2.604651162790698</v>
       </c>
       <c r="AK4">
-        <v>-0.08344549125168237</v>
+        <v>-0.3115438108484006</v>
       </c>
       <c r="AL4">
-        <v>0.018</v>
+        <v>0.012</v>
       </c>
       <c r="AM4">
-        <v>0.018</v>
+        <v>0.012</v>
       </c>
       <c r="AO4">
-        <v>-16</v>
+        <v>-46.41666666666667</v>
       </c>
       <c r="AQ4">
-        <v>-16</v>
+        <v>-46.41666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -948,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NORD.investments A/S (CPSE:NORD)</t>
+          <t>NORD.investments Fondsmæglerselskab A/S (CPSE:NORD)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,22 +954,22 @@
         </is>
       </c>
       <c r="G5">
-        <v>3.053221288515406</v>
+        <v>-2.251908396946565</v>
       </c>
       <c r="H5">
-        <v>3.053221288515406</v>
+        <v>-2.251908396946565</v>
       </c>
       <c r="I5">
-        <v>3.945064338462865</v>
+        <v>-2.106803902415494</v>
       </c>
       <c r="J5">
-        <v>3.945064338462865</v>
+        <v>-2.106803902415494</v>
       </c>
       <c r="K5">
-        <v>-2</v>
+        <v>-1.58</v>
       </c>
       <c r="L5">
-        <v>5.602240896358544</v>
+        <v>-2.010178117048346</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -996,67 +993,64 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>9.01</v>
+        <v>5.95</v>
       </c>
       <c r="V5">
-        <v>0.6482014388489208</v>
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="W5">
+        <v>-0.1771300448430493</v>
       </c>
       <c r="X5">
-        <v>0.04387609615994809</v>
-      </c>
-      <c r="Z5">
-        <v>-184.0354024606664</v>
-      </c>
-      <c r="AA5">
-        <v>-726.031503262236</v>
+        <v>0.07246641599770315</v>
+      </c>
+      <c r="Y5">
+        <v>-0.2495964608407525</v>
       </c>
       <c r="AB5">
-        <v>0.04387334897279225</v>
-      </c>
-      <c r="AC5">
-        <v>-726.0753766112088</v>
+        <v>0.07245268461371759</v>
       </c>
       <c r="AD5">
         <v>0</v>
       </c>
       <c r="AE5">
-        <v>0.001939844156215004</v>
+        <v>0.004739336492890996</v>
       </c>
       <c r="AF5">
-        <v>0.001939844156215004</v>
+        <v>0.004739336492890996</v>
       </c>
       <c r="AG5">
-        <v>-9.008060155843785</v>
+        <v>-5.945260663507109</v>
       </c>
       <c r="AH5">
-        <v>0.0001395376600647881</v>
+        <v>0.0004644250417982538</v>
       </c>
       <c r="AI5">
-        <v>0.0002174240344699906</v>
+        <v>0.0007529043284469842</v>
       </c>
       <c r="AJ5">
-        <v>-1.841408611474358</v>
+        <v>-1.397326649958229</v>
       </c>
       <c r="AK5">
-        <v>102.2943926175165</v>
+        <v>-17.24566950783613</v>
       </c>
       <c r="AL5">
-        <v>0.016</v>
+        <v>0.004</v>
       </c>
       <c r="AM5">
-        <v>0.016</v>
+        <v>0.004</v>
       </c>
       <c r="AN5">
         <v>-0</v>
       </c>
       <c r="AO5">
-        <v>-88.125</v>
+        <v>-414.9999999999999</v>
       </c>
       <c r="AP5">
-        <v>6.397769997048143</v>
+        <v>3.636245054132788</v>
       </c>
       <c r="AQ5">
-        <v>-88.125</v>
+        <v>-414.9999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/denmark/denmark_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_investments_asset_management.xlsx
@@ -587,47 +587,41 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.0638</v>
-      </c>
-      <c r="E2">
-        <v>-0.123</v>
-      </c>
       <c r="G2">
-        <v>-0.3528708133971292</v>
+        <v>-0.1994241228537912</v>
       </c>
       <c r="H2">
-        <v>-0.3528708133971292</v>
+        <v>-0.1994241228537912</v>
       </c>
       <c r="I2">
-        <v>0.2625702018942228</v>
+        <v>0.6832930271026427</v>
       </c>
       <c r="J2">
-        <v>0.2500981173042472</v>
+        <v>0.6703191088665166</v>
       </c>
       <c r="K2">
-        <v>0.7940000000000002</v>
+        <v>6.709999999999999</v>
       </c>
       <c r="L2">
-        <v>0.1582934609250399</v>
+        <v>0.7155806761224272</v>
       </c>
       <c r="M2">
-        <v>0.889</v>
+        <v>1.92</v>
       </c>
       <c r="N2">
-        <v>0.01234722222222222</v>
+        <v>0.02272996330058009</v>
       </c>
       <c r="O2">
-        <v>1.119647355163728</v>
+        <v>0.286140089418778</v>
       </c>
       <c r="P2">
-        <v>0.889</v>
+        <v>1.92</v>
       </c>
       <c r="Q2">
-        <v>0.01234722222222222</v>
+        <v>0.02272996330058009</v>
       </c>
       <c r="R2">
-        <v>1.119647355163728</v>
+        <v>0.286140089418778</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>10.21</v>
+        <v>8.49</v>
       </c>
       <c r="V2">
-        <v>0.1418055555555556</v>
+        <v>0.1005090564697526</v>
       </c>
       <c r="W2">
-        <v>-0.02273291925465838</v>
+        <v>-0.1251325556733828</v>
       </c>
       <c r="X2">
-        <v>0.07246641599770315</v>
+        <v>0.06232327055348564</v>
       </c>
       <c r="Y2">
-        <v>-0.09519933525236153</v>
+        <v>-0.1874558262268685</v>
       </c>
       <c r="Z2">
-        <v>0.0572857779148251</v>
+        <v>0.1380720724357142</v>
       </c>
       <c r="AA2">
-        <v>-0.03748317631224764</v>
+        <v>0.01446453407510431</v>
       </c>
       <c r="AB2">
-        <v>0.07245268461371759</v>
+        <v>0.06230489745680006</v>
       </c>
       <c r="AC2">
-        <v>-0.1099373953529525</v>
+        <v>-0.04784385446069732</v>
       </c>
       <c r="AD2">
-        <v>13.9</v>
+        <v>6.87</v>
       </c>
       <c r="AE2">
-        <v>0.004739336492890996</v>
+        <v>0.003806424292599835</v>
       </c>
       <c r="AF2">
-        <v>13.90473933649289</v>
+        <v>6.8738064242926</v>
       </c>
       <c r="AG2">
-        <v>3.694739336492891</v>
+        <v>-1.6161935757074</v>
       </c>
       <c r="AH2">
-        <v>0.1618623075267987</v>
+        <v>0.07525202521519328</v>
       </c>
       <c r="AI2">
-        <v>0.1779812573403088</v>
+        <v>0.08740429458878943</v>
       </c>
       <c r="AJ2">
-        <v>0.04881104511197695</v>
+        <v>-0.01950657001117012</v>
       </c>
       <c r="AK2">
-        <v>0.05440261381534277</v>
+        <v>-0.02303786006895487</v>
       </c>
       <c r="AL2">
-        <v>0.344</v>
+        <v>0.501</v>
       </c>
       <c r="AM2">
-        <v>0.344</v>
+        <v>0.501</v>
       </c>
       <c r="AN2">
-        <v>-8.501529051987768</v>
+        <v>-6.897590361445784</v>
       </c>
       <c r="AO2">
-        <v>3.816860465116278</v>
+        <v>12.78243512974052</v>
       </c>
       <c r="AP2">
-        <v>-2.259779410699016</v>
+        <v>1.622684312959237</v>
       </c>
       <c r="AQ2">
-        <v>3.816860465116278</v>
+        <v>12.78243512974052</v>
       </c>
     </row>
     <row r="3">
@@ -721,12 +715,6 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.0638</v>
-      </c>
-      <c r="E3">
-        <v>-0.123</v>
-      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -734,34 +722,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.8345153664302599</v>
+        <v>0.8651817116060961</v>
       </c>
       <c r="J3">
-        <v>0.7155969267139479</v>
+        <v>0.8158992090462552</v>
       </c>
       <c r="K3">
-        <v>2.74</v>
+        <v>8.94</v>
       </c>
       <c r="L3">
-        <v>0.6477541371158392</v>
+        <v>1.048065650644783</v>
       </c>
       <c r="M3">
-        <v>0.889</v>
+        <v>1.92</v>
       </c>
       <c r="N3">
-        <v>0.01514480408858603</v>
+        <v>0.025</v>
       </c>
       <c r="O3">
-        <v>0.3244525547445255</v>
+        <v>0.2147651006711409</v>
       </c>
       <c r="P3">
-        <v>0.889</v>
+        <v>1.92</v>
       </c>
       <c r="Q3">
-        <v>0.01514480408858603</v>
+        <v>0.025</v>
       </c>
       <c r="R3">
-        <v>0.3244525547445255</v>
+        <v>0.2147651006711409</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,67 +758,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.02</v>
+        <v>7.43</v>
       </c>
       <c r="V3">
-        <v>0.03441226575809199</v>
+        <v>0.09674479166666666</v>
       </c>
       <c r="W3">
-        <v>0.04781849912739965</v>
+        <v>0.1843298969072165</v>
       </c>
       <c r="X3">
-        <v>0.07867021636335089</v>
+        <v>0.0639486496140301</v>
       </c>
       <c r="Y3">
-        <v>-0.03085171723595124</v>
+        <v>0.1203812472931864</v>
       </c>
       <c r="Z3">
-        <v>0.05818351879616512</v>
+        <v>0.1412719443524346</v>
       </c>
       <c r="AA3">
-        <v>0.04163594723593899</v>
+        <v>0.115263667657578</v>
       </c>
       <c r="AB3">
-        <v>0.07067173967670383</v>
+        <v>0.0615826904524622</v>
       </c>
       <c r="AC3">
-        <v>-0.02903579244076484</v>
+        <v>0.05368097720511577</v>
       </c>
       <c r="AD3">
-        <v>13.9</v>
+        <v>6.87</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>13.9</v>
+        <v>6.87</v>
       </c>
       <c r="AG3">
-        <v>11.88</v>
+        <v>-0.5599999999999996</v>
       </c>
       <c r="AH3">
-        <v>0.1914600550964187</v>
+        <v>0.08210828253854428</v>
       </c>
       <c r="AI3">
-        <v>0.2227564102564103</v>
+        <v>0.1009255178492728</v>
       </c>
       <c r="AJ3">
-        <v>0.1683196372910173</v>
+        <v>-0.007345225603357813</v>
       </c>
       <c r="AK3">
-        <v>0.1967538920172243</v>
+        <v>-0.00923482849604221</v>
       </c>
       <c r="AL3">
-        <v>0.328</v>
+        <v>0.479</v>
       </c>
       <c r="AM3">
-        <v>0.328</v>
+        <v>0.479</v>
       </c>
       <c r="AO3">
-        <v>10.76219512195122</v>
+        <v>15.4070981210856</v>
       </c>
       <c r="AQ3">
-        <v>10.76219512195122</v>
+        <v>15.4070981210856</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +838,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>-0.366</v>
+        <v>-1.18</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -874,31 +862,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.24</v>
+        <v>1.06</v>
       </c>
       <c r="V4">
-        <v>0.7225806451612904</v>
+        <v>0.3557046979865772</v>
       </c>
       <c r="W4">
-        <v>-0.02273291925465838</v>
+        <v>-0.1251325556733828</v>
       </c>
       <c r="X4">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y4">
-        <v>-0.09518713829536324</v>
+        <v>-0.1874409442091844</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.03748317631224764</v>
+        <v>0.01446453407510431</v>
       </c>
       <c r="AB4">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC4">
-        <v>-0.1099373953529525</v>
+        <v>-0.04784385446069732</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -910,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-2.24</v>
+        <v>-1.06</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -919,22 +907,22 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-2.604651162790698</v>
+        <v>-0.5520833333333334</v>
       </c>
       <c r="AK4">
-        <v>-0.3115438108484006</v>
+        <v>-0.2710997442455244</v>
       </c>
       <c r="AL4">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AM4">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AO4">
-        <v>-46.41666666666667</v>
+        <v>9.454545454545455</v>
       </c>
       <c r="AQ4">
-        <v>-46.41666666666667</v>
+        <v>9.454545454545455</v>
       </c>
     </row>
     <row r="5">
@@ -954,22 +942,22 @@
         </is>
       </c>
       <c r="G5">
-        <v>-2.251908396946565</v>
+        <v>-2.207792207792208</v>
       </c>
       <c r="H5">
-        <v>-2.251908396946565</v>
+        <v>-2.207792207792208</v>
       </c>
       <c r="I5">
-        <v>-2.106803902415494</v>
+        <v>-1.271264799124581</v>
       </c>
       <c r="J5">
-        <v>-2.106803902415494</v>
+        <v>-1.271264799124581</v>
       </c>
       <c r="K5">
-        <v>-1.58</v>
+        <v>-1.05</v>
       </c>
       <c r="L5">
-        <v>-2.010178117048346</v>
+        <v>-1.239669421487603</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -993,64 +981,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>0.5833333333333334</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>-0.1771300448430493</v>
+        <v>-0.1669316375198728</v>
       </c>
       <c r="X5">
-        <v>0.07246641599770315</v>
+        <v>0.06232327055348564</v>
       </c>
       <c r="Y5">
-        <v>-0.2495964608407525</v>
+        <v>-0.2292549080733585</v>
+      </c>
+      <c r="Z5">
+        <v>2.463595617047437</v>
+      </c>
+      <c r="AA5">
+        <v>-3.131882387230008</v>
       </c>
       <c r="AB5">
-        <v>0.07245268461371759</v>
+        <v>0.06230489745680006</v>
+      </c>
+      <c r="AC5">
+        <v>-3.194187284686808</v>
       </c>
       <c r="AD5">
         <v>0</v>
       </c>
       <c r="AE5">
-        <v>0.004739336492890996</v>
+        <v>0.003806424292599835</v>
       </c>
       <c r="AF5">
-        <v>0.004739336492890996</v>
+        <v>0.003806424292599835</v>
       </c>
       <c r="AG5">
-        <v>-5.945260663507109</v>
+        <v>0.003806424292599835</v>
       </c>
       <c r="AH5">
-        <v>0.0004644250417982538</v>
+        <v>0.000810946159368619</v>
       </c>
       <c r="AI5">
-        <v>0.0007529043284469842</v>
+        <v>0.0006792569200996877</v>
       </c>
       <c r="AJ5">
-        <v>-1.397326649958229</v>
+        <v>0.000810946159368619</v>
       </c>
       <c r="AK5">
-        <v>-17.24566950783613</v>
+        <v>0.0006792569200996877</v>
       </c>
       <c r="AL5">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="AM5">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="AN5">
         <v>-0</v>
       </c>
       <c r="AO5">
-        <v>-414.9999999999999</v>
+        <v>-98.18181818181819</v>
       </c>
       <c r="AP5">
-        <v>3.636245054132788</v>
+        <v>-0.003821711137148429</v>
       </c>
       <c r="AQ5">
-        <v>-414.9999999999999</v>
+        <v>-98.18181818181819</v>
       </c>
     </row>
   </sheetData>
